--- a/cars.xlsx
+++ b/cars.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A985F083-8292-4ACE-A11E-A1BF374F7782}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B783A0-CECF-460E-8F5D-ADBE18ED5E83}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="27948" windowHeight="12252" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="75">
   <si>
     <t>产品型号</t>
   </si>
@@ -258,6 +258,9 @@
   <si>
     <t>汽油</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://q0.itc.cn/q_70/images03/20260113/ab41668d8b0f4a0784b614533ccaccfd.jpeg</t>
   </si>
 </sst>
 </file>
@@ -363,12 +366,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -380,6 +377,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -875,107 +878,107 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="O1" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="P1" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="Q1" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="R1" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="S1" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="T1" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="U1" s="11" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7" t="s">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="12"/>
+      <c r="T2" s="12"/>
+      <c r="U2" s="12"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="7" t="s">
         <v>49</v>
       </c>
       <c r="D3" s="3" t="s">
@@ -1014,13 +1017,13 @@
       <c r="U3" s="2"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="8" t="s">
         <v>52</v>
       </c>
       <c r="D4" s="5" t="s">
@@ -1047,7 +1050,9 @@
       <c r="K4" s="1">
         <v>135500</v>
       </c>
-      <c r="L4" s="2"/>
+      <c r="L4" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1059,13 +1064,13 @@
       <c r="U4" s="2"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="8" t="s">
         <v>53</v>
       </c>
       <c r="D5" s="5" t="s">
@@ -1092,29 +1097,29 @@
       <c r="K5" s="1">
         <v>95000</v>
       </c>
-      <c r="L5" s="11" t="s">
+      <c r="L5" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="M5" s="12" t="s">
+      <c r="M5" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="N5" s="11"/>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="11"/>
-      <c r="S5" s="11"/>
-      <c r="T5" s="11"/>
-      <c r="U5" s="11"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="8" t="s">
         <v>72</v>
       </c>
       <c r="D6" s="5" t="s">
@@ -1153,10 +1158,10 @@
       <c r="U6" s="2"/>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="8" t="s">
         <v>73</v>
       </c>
       <c r="C7" s="5" t="s">
@@ -1198,10 +1203,10 @@
       <c r="U7" s="2"/>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="8" t="s">
         <v>73</v>
       </c>
       <c r="C8" s="5" t="s">
@@ -1243,10 +1248,10 @@
       <c r="U8" s="2"/>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="8" t="s">
         <v>73</v>
       </c>
       <c r="C9" s="5" t="s">
@@ -1288,10 +1293,10 @@
       <c r="U9" s="2"/>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="8" t="s">
         <v>73</v>
       </c>
       <c r="C10" s="5" t="s">
@@ -1333,10 +1338,10 @@
       <c r="U10" s="2"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="8" t="s">
         <v>73</v>
       </c>
       <c r="C11" s="5" t="s">
@@ -1378,10 +1383,10 @@
       <c r="U11" s="2"/>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="8" t="s">
         <v>73</v>
       </c>
       <c r="C12" s="5" t="s">
@@ -1423,10 +1428,10 @@
       <c r="U12" s="2"/>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="8" t="s">
         <v>73</v>
       </c>
       <c r="C13" s="5" t="s">
@@ -1468,10 +1473,10 @@
       <c r="U13" s="2"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="8" t="s">
         <v>73</v>
       </c>
       <c r="C14" s="5" t="s">
@@ -1514,6 +1519,16 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
     <mergeCell ref="R1:R2"/>
     <mergeCell ref="S1:S2"/>
     <mergeCell ref="T1:T2"/>
@@ -1524,17 +1539,7 @@
     <mergeCell ref="O1:O2"/>
     <mergeCell ref="P1:P2"/>
     <mergeCell ref="Q1:Q2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="K1:K2"/>
     <mergeCell ref="L1:L2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
